--- a/examples/sixdrive12resp/results/case/profiles/profile_28_optdiag_trim.xlsx
+++ b/examples/sixdrive12resp/results/case/profiles/profile_28_optdiag_trim.xlsx
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1e-6,0.05,20,1.0,0.95,6,-9.0,0,2,2.0,0.5,3.0,0.5,0.5</t>
+          <t>1e-6,0.05,20,1.0,0.95,6,-9.0,0,2,2.0,0.5,3.0,0.5,0.5,0.5</t>
         </is>
       </c>
     </row>
